--- a/data/availability/projects/la-vista-developments/la-vista-6.xlsx
+++ b/data/availability/projects/la-vista-developments/la-vista-6.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Updated inventory for la-vista-6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1046,7 +1056,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1107,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1168,7 +1178,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1229,7 +1239,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029-01-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
